--- a/medford_mammografy.xlsx
+++ b/medford_mammografy.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Маммографы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Siemens, GE, IMS, Fujifilm — всего 20 позиций.</t>
+          <t>Маммографы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Siemens, GE, IMS, Fujifilm.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_mammografy.xlsx
+++ b/medford_mammografy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать маммографы для клиники?</t>
+          <t>Чем цифровой маммограф отличается от аналогового?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Тип приемника, Формат приемника, см, Мощность генератора, кВт). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Цифровой маммограф фиксирует изображение на детектор, даёт высокую чёткость, снижает лучевую нагрузку и поддерживает архив и обработку снимков. Аналоговый использует плёнку или кассеты и обычно дешевле. В каталоге есть обе категории, а также комбинированные модели с цифровым и аналоговым приёмником.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Что даёт томосинтез?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Томосинтез позволяет делать послойные снимки молочной железы, что помогает точнее оценивать сложные патологии по сравнению с обычной 2D-маммографией. Функция удорожает систему, поэтому её выбирают под задачи углублённой диагностики. В каталоге есть модели с томосинтезом — IMS Giotto TOMO и МТЛ «Маммо-5МТ».</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какой формат приёмника выбрать?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Siemens, GE, IMS, Fujifilm. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Формат приёмника определяет площадь захвата: в каталоге это 18х24 и 24х30 см, часть аппаратов поддерживает оба. Формат 24х30 см подходит для большинства пациенток и удобен при потоке. Оптимальный формат под задачи кабинета уточняют при подборе модели.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Можно ли делать биопсию на маммографе?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Да, при наличии биопсийной приставки. Например, МТЛ «Маммо-5МТ» поставляется в версии с приставкой для стереотаксической пункции под контролем аппарата. Если планируете инвазивную диагностику, выбирайте систему с поддержкой биопсийного модуля или возможностью его дооснащения. Необходимость и объём биопсии в конкретном случае определяет врач.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Нужно ли РУ Росздравнадзора и особые требования к помещению?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Да. Маммограф — рентгеновское медицинское изделие, для применения нужно действующее регистрационное удостоверение Росздравнадзора. Кроме того, размещение рентгеновского аппарата требует соблюдения норм радиационной безопасности и подготовки помещения. Наличие РУ, тип детектора и требования по помещению уточняйте до покупки, чтобы заранее оценить готовность кабинета.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Какая мощность генератора нужна?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Мощность генератора в каталоге — от 3,3 до 10 кВт. Для скрининга с высоким потоком предпочтительнее более мощный генератор: короче экспозиция и стабильнее работа. Для небольшого кабинета достаточно моделей нижней части диапазона. Подбор ведут под ожидаемую нагрузку.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>mammografy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Есть ли отечественные маммографы?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Да. В каталоге представлены российские модели: ADVIN (МАММОСКАН, МАММОЭКСПЕРТ), РенМедПром (ОМИКРОН и ОМИКРОН Плюс), МТЛ «Маммо-5МТ» в версиях универсальной, с биопсией и с томосинтезом, а также Медикал-Сервис DiAR Mammo. Наряду с ними — импортные Siemens, Fujifilm, IMS Giotto, GENORAY.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>mammografy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2072,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Маммографы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Siemens, GE, IMS, Fujifilm.</t>
+          <t>Маммографы — это рентгеновские аппараты для лучевой диагностики молочной железы. В каталоге представлены цифровые системы (Siemens Mammomat Fusion и Revelation, Fujifilm AMULET Innovality, GENORAY DMX-600), аналоговые и комбинированные модели (Siemens Mammomat Select, Italray, Bemems Pinkview-AT), аппараты с томосинтезом (IMS Giotto TOMO, МТЛ «Маммо-5МТ» с томосинтезом) и приставками для биопсии. Формат приёмника — 18х24 и 24х30 см, мощность генератора — от 3,3 до 10 кВт. Есть отечественные решения ADVIN, РенМедПром и МТЛ.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2356,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Виды маммографов</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2644,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое маммографы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4430,203 +4506,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Виды маммографов</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Особенность</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Тип приемника</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Формат приемника, см</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Мощность генератора, кВт</t>
+          <t>Пример моделей</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Маммограф Siemens Mammomat Fusion</t>
+          <t>Цифровой</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>Высокая чёткость, ниже лучевая нагрузка, архив</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Цифровой</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>24х30</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>Siemens Mammomat Fusion, Fujifilm AMULET, GENORAY DMX-600</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Маммограф ADVIN МАММОСКАН</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+          <t>Аналоговый / комбинированный</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Плёнка/кассеты, дешевле</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Цифровой</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>24х30</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Siemens Mammomat Select, Italray, Bemems Pinkview-AT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Маммограф ADVIN МАММОЭКСПЕРТ</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+          <t>С томосинтезом</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Послойные снимки для сложных случаев</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Цифровой</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>24х30</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>IMS Giotto TOMO, МТЛ «Маммо-5МТ» с томосинтезом</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Маммограф Medi-Future Brestige</t>
+          <t>С биопсией</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>Приставка для стереотаксической пункции</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Цифровой</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>24х30</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Маммограф IMS Giotto M</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Аналоговый</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>18х24, 24х30</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Маммограф РенМедПром ОМИКРОН Плюс</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Цифровой</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>24х30</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>4.8</t>
+          <t>МТЛ «Маммо-5МТ» с приставкой для биопсии</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4638,7 +4620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4964,12 +4946,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите тип приёмника</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается маммографы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Цифровые маммографы дают высокую чёткость снимка и снижают лучевую нагрузку, поддерживают архив и обработку. Аналоговые работают на плёнке/кассетах и дешевле. В каталоге есть цифровые (Siemens Mammomat Fusion, Fujifilm AMULET) и аналоговые/комбинированные (Siemens Select, Italray, Bemems Pinkview-AT). Выбор задаёт формат работы.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5009,12 +4991,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Решите, нужен ли томосинтез</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Томосинтез делает послойные снимки железы и помогает в сложных диагностических случаях, но удорожает систему. Если задача — углублённая диагностика, выбирают модели с томосинтезом: IMS Giotto TOMO, МТЛ «Маммо-5МТ» с томосинтезом. Для базового скрининга достаточно цифрового аппарата без томосинтеза.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5054,12 +5036,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Подберите формат приёмника</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Тип приемника, Формат приемника, см, Мощность генератора, кВт. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Формат определяет площадь захвата за экспозицию. В каталоге приёмники 18х24 и 24х30 см, часть моделей поддерживает оба. Формат 24х30 см закрывает большинство пациенток и удобен для потока. Уточните доступные форматы у конкретной модели под ваши задачи.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5099,12 +5081,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените мощность генератора</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Siemens, GE, IMS, Fujifilm.</t>
+          <t>Мощность генератора в каталоге — от 3,3 до 10 кВт. Более мощный генератор сокращает время экспозиции и стабильнее при потоке. Подбирайте мощность под ожидаемую нагрузку кабинета; для скрининговых центров с высоким потоком предпочтительнее верхняя часть диапазона.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5144,12 +5126,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Заложите биопсию, если нужна</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Часть моделей поставляется с приставкой для стереотаксической биопсии — например, МТЛ «Маммо-5МТ» с приставкой для биопсии. Если планируете инвазивную диагностику, выбирайте систему с поддержкой биопсийного модуля или возможностью его дооснащения. Уточните состав приставки.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5189,12 +5171,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Проверьте РУ, детектор и рабочую станцию</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Маммограф — рентгеновское медицинское изделие: запросите действующее РУ Росздравнадзора. Для цифровых систем уточните тип детектора, рабочую станцию, программное обеспечение и требования к помещению по радиационной безопасности. Эти позиции определяют готовность аппарата к работе и легальность применения; размещение рентгеновского аппарата дополнительно требует согласования по нормам защиты.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5244,7 +5226,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Маммографы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Siemens, GE, IMS, Fujifilm. При выборе обращают внимание на тип приемника, формат приемника, мощность генератора, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>В маммографе первым делом определяют задачу: скрининг с высоким потоком, диагностика или биопсия. Для потока берут цифровую систему — она даёт чёткость и снижает лучевую нагрузку. Томосинтез нужен там, где важны послойные снимки при сложных случаях, но он удорожает аппарат. Формат приёмника 24х30 см закрывает большинство пациенток. При покупке я всегда сверяю действующее РУ и комплектность генератора и рабочей станции.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5528,13 +5510,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое маммографы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Маммографы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Siemens, GE, IMS, Fujifilm. Подберём вариант под задачи вашего отделения.</t>
+          <t>Маммограф — рентгеновский аппарат для лучевой диагностики молочной железы. По типу приёмника различают цифровые, аналоговые и комбинированные модели, отдельно выделяют системы с томосинтезом для послойных снимков и версии с приставкой для стереотаксической биопсии. Цифровые аппараты дают высокую чёткость и снижают лучевую нагрузку. Ключевые параметры выбора: тип и формат приёмника (в каталоге 18х24 и 24х30 см), мощность генератора (3,3–10 кВт) и наличие томосинтеза. Есть импортные и отечественные модели; аппарат требует РУ Росздравнадзора и соблюдения норм радиационной безопасности.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5571,13 +5553,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое маммограф</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Тип приемника, Формат приемника, см, Мощность генератора, кВт), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Маммограф — рентгеновский аппарат для лучевой диагностики молочной железы. Он позволяет выявлять патологии на ранних стадиях, включая непальпируемые образования. Современные цифровые системы дают высокую чёткость снимка и снижают лучевую нагрузку, поддерживают архивирование и обработку изображений, а модели с томосинтезом делают послойные снимки.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5614,13 +5596,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Виды маммографов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По типу приёмника маммографы делят на цифровые, аналоговые и комбинированные. Отдельно выделяют системы с томосинтезом для послойных снимков и версии с приставкой для стереотаксической биопсии. Скрининговые системы рассчитаны на высокую пропускную способность. Такая классификация помогает подобрать аппарат под профиль кабинета.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5657,13 +5639,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Характеристики при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Ключевые параметры: тип приёмника (цифровой снижает лучевую нагрузку), формат приёмника (18х24 и 24х30 см), мощность генератора (в каталоге 3,3–10 кВт), наличие томосинтеза и биопсийной приставки. Для цифровых систем значимы тип детектора, рабочая станция и ПО. Подбор ведут под поток и задачи.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5680,6 +5662,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Импортные и отечественные модели</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Каталог совмещает импортные аппараты Siemens (Mammomat Fusion, Revelation, Select), Fujifilm AMULET Innovality, IMS Giotto (M, 3D, TOMO), GENORAY DMX-600 и отечественные решения ADVIN, РенМедПром ОМИКРОН, МТЛ «Маммо-5МТ» и DiAR Mammo. Это покрывает диапазон от базового скрининга до диагностики с томосинтезом и биопсией.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>mammografy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
